--- a/output/pdf_financials_xlsx/AGX.xlsx
+++ b/output/pdf_financials_xlsx/AGX.xlsx
@@ -6033,22 +6033,22 @@
         <v>0</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.026364</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>11.420125</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.391036</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>9.968956</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>10.518746</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>14.188802</v>
       </c>
     </row>
     <row r="93">
@@ -10810,7 +10810,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -16872,7 +16876,11 @@
           <t>Reserves 11,420,124</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AGX.xlsx
+++ b/output/pdf_financials_xlsx/AGX.xlsx
@@ -1062,31 +1062,31 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.015476</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.015957</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.012183</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000508</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1.4e-05</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>1.4e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000183</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>8.8e-05</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000242</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0.045649</v>
@@ -2024,31 +2024,31 @@
         <v>-1.706052</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.606089</v>
+        <v>-3.621565</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.06039</v>
+        <v>-1.076347</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.358783</v>
+        <v>-3.370966</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-6.28679</v>
+        <v>-6.287298</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.498511</v>
+        <v>-3.498525</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6.712898</v>
+        <v>6.712884</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.487677</v>
+        <v>-0.48786</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.331877</v>
+        <v>-0.331965</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.377516</v>
+        <v>-0.377758</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-11.303691</v>
@@ -2140,31 +2140,31 @@
         <v>-1.706052</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.606089</v>
+        <v>-3.621565</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.06039</v>
+        <v>-1.076347</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.358783</v>
+        <v>-3.370966</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.28679</v>
+        <v>-6.287298</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.498511</v>
+        <v>-3.498525</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>6.712898</v>
+        <v>6.712884</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.487677</v>
+        <v>-0.48786</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.331877</v>
+        <v>-0.331965</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.377516</v>
+        <v>-0.377758</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-11.303691</v>
@@ -2443,52 +2443,52 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.901362</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.372629</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.892187</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.83023</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.814948</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.333157</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.030547</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.162937</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.022171</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.002086</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.034886</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.505888</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.023979</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.484902</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.784429</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>10.052225</v>
       </c>
     </row>
     <row r="35">
@@ -2563,52 +2563,52 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.901362</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.372629</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.892187</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.83023</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.814948</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.333157</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.030547</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.162937</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.022171</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.002086</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.034886</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.505888</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.023979</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.484902</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.784429</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>10.052225</v>
       </c>
     </row>
     <row r="37">
@@ -3283,52 +3283,52 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.910924</v>
+        <v>0.009561999999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.397371</v>
+        <v>0.024742</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.90956</v>
+        <v>0.017373</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.866256</v>
+        <v>0.036026</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.918154</v>
+        <v>0.103206</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.408275</v>
+        <v>0.075118</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.031503</v>
+        <v>0.000956</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.326687</v>
+        <v>0.16375</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.026921</v>
+        <v>0.00475</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.002086</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.034031</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.977653</v>
+        <v>0.471765</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.248439</v>
+        <v>0.22446</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.858798</v>
+        <v>0.373896</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.005013</v>
+        <v>0.220584</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>10.282422</v>
+        <v>0.230197</v>
       </c>
     </row>
     <row r="49">
@@ -7851,19 +7851,19 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.209957</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.202832</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.318484</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0298</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0258</v>
       </c>
     </row>
     <row r="125">
@@ -7909,19 +7909,19 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.209957</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.202832</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.318484</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0298</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0258</v>
       </c>
     </row>
     <row r="126">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -19656,7 +19656,11 @@
           <t>Reclamation deposits (Note 8)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -20462,7 +20466,11 @@
           <t>Reclamation deposits (Note 9)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -22577,7 +22585,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -24076,7 +24088,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -24177,7 +24189,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -25292,7 +25308,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -26007,7 +26023,11 @@
           <t>RECLAMATION DEPOSIT (Note 6)</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -28598,7 +28618,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -30182,7 +30206,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -40386,7 +40414,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -45356,7 +45388,11 @@
           <t>Increase in reclamation deposit 7</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -47568,7 +47604,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -69321,7 +69361,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
@@ -72238,7 +72278,7 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
